--- a/data/market_excel/market_final_SFA반도체.xlsx
+++ b/data/market_excel/market_final_SFA반도체.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SFA반도체는 AI 투자 확대에 따른 반도체 후공정 산업의 높은 성장 잠재력과 최근 주가 상승 모멘텀을 바탕으로 긍정적인 전망을 보입니다. 그러나 불확실한 거시 경제 환경과 경쟁 심화 가능성은 보유 의견을 유지하는 주요 근거입니다.</t>
+          <t>AI 반도체 후공정 산업의 높은 성장 잠재력과 최근 주가 모멘텀은 긍정적입니다. 그러나 거시 경제 불확실성과 경쟁 심화 가능성을 고려하여 '보유' 의견을 제시합니다.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SFA반도체는 AI 투자 확대에 따른 반도체 후공정 산업의 높은 성장 잠재력과 최근 주가 상승 모멘텀을 바탕으로 긍정적인 전망을 보입니다. 그러나 불확실한 거시 경제 환경과 경쟁 심화 가능성은 보유 의견을 유지하는 주요 근거입니다.</t>
+          <t>AI 반도체 후공정 산업의 높은 성장 잠재력과 최근 주가 모멘텀은 긍정적입니다. 그러나 거시 경제 불확실성과 경쟁 심화 가능성을 고려하여 '보유' 의견을 제시합니다.</t>
         </is>
       </c>
     </row>
